--- a/exploraciones.xlsx
+++ b/exploraciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://farmacity-my.sharepoint.com/personal/i_link_farmacity_com_ar/Documents/Escritorio/Personal/Maestria/Sistemas de recomendación/competencia_quelibroleo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="11_AD4D2F04E46CFB4ACB3E20BFE557DAF2693EDF1D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D82E8D0-9EC6-4444-9E1B-8606B4961D32}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="11_AD4D2F04E46CFB4ACB3E20BFE557DAF2693EDF1D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5577F1B-D7D8-4BCD-8C76-B42F496523D3}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -728,16 +728,16 @@
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" s="6">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="C2" s="13">
         <v>6.5500000000000003E-2</v>
       </c>
       <c r="D2" s="12">
-        <v>1.67E-2</v>
+        <v>2.8000000000000001E-2</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>21</v>
